--- a/DateBase/orders/Dang Nguyen 195_2026-5-3.xlsx
+++ b/DateBase/orders/Dang Nguyen 195_2026-5-3.xlsx
@@ -872,6 +872,9 @@
       <c r="G2" t="str">
         <v>010975101055510551052056530305201055555553105105510105325105</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
